--- a/artfynd/A 4796-2025 artfynd.xlsx
+++ b/artfynd/A 4796-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,384 +796,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>90985115</v>
-      </c>
-      <c r="B3" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>221725</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ögonpyrola</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>125 m OSO om gården Dryp, Boh</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>296355.6177103333</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6498825.359749936</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Munkedal</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Svarteborg</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2002-08-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2002-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skogsklädd ravin</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Sven Bergqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>90985117</v>
-      </c>
-      <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>125 m OSO om gården Dryp, Boh</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>296355.6177103333</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6498825.359749936</v>
-      </c>
-      <c r="S4" t="n">
-        <v>100</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Munkedal</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Svarteborg</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2002-08-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2002-08-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Skogsklädd ravin</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Sven Bergqvist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>90985113</v>
-      </c>
-      <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>125 m OSO om gården Dryp, Boh</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>296355.6177103333</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6498825.359749936</v>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Munkedal</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Svarteborg</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2002-08-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2002-08-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bohusläns flora - 2011.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Skogsklädd ravin</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Evastina Blomgren</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Sven Bergqvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
